--- a/data/trans_dic/IP16B98-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero otros medicamentos recetados por el médico</t>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -583,7 +584,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,17 +632,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 100,0</t>
+          <t>27,31; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,19 +652,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,56; 100,0</t>
+          <t>35,19; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,34 +717,34 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,25; 100,0</t>
+          <t>40,96; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,36; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -951,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1031,17 +1032,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1051,19 +1052,19 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,31; 100,0</t>
+          <t>51,82; 100,0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1111,17 +1112,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1131,12 +1132,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1191,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,86; 100,0</t>
+          <t>44,49; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,51; 100,0</t>
+          <t>23,07; 100,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,71; 94,07</t>
+          <t>45,21; 93,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1271,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,62; 100,0</t>
+          <t>74,38; 100,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88,2; 100,0</t>
+          <t>88,45; 100,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,22; 100,0</t>
+          <t>74,58; 100,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,44; 100,0</t>
+          <t>80,27; 100,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>82,25; 98,26</t>
+          <t>81,86; 97,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>87,49; 98,77</t>
+          <t>86,74; 98,77</t>
         </is>
       </c>
     </row>
@@ -1325,4 +1326,1182 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>941; 3446</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2000</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1916; 5445</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>670; 2623</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2108; 5146</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6677</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5167</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4356</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>827; 3822</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2628; 5071</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5290</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3967</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4572</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>6976</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2024; 4549</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1254; 5435</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>4513; 9379</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>15589</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>21114</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21576</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>36622</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>42690</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>12494; 16798</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>19164; 21668</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>17006; 22803</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>18540; 23098</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>32418; 38513</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>38830; 44216</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B98-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Provincia-trans_dic.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,31; 100,0</t>
+          <t>23,37; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,19; 100,0</t>
+          <t>34,08; 100,0</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,82; 100,0</t>
+          <t>41,14; 100,0</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,49; 100,0</t>
+          <t>44,27; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,21; 93,94</t>
+          <t>45,11; 93,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,38; 100,0</t>
+          <t>77,57; 100,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88,45; 100,0</t>
+          <t>86,8; 100,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,27; 100,0</t>
+          <t>80,45; 100,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>81,86; 97,25</t>
+          <t>82,03; 97,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,74; 98,77</t>
+          <t>86,6; 98,76</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>941; 3446</t>
+          <t>805; 3446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1916; 5445</t>
+          <t>1855; 5445</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2628; 5071</t>
+          <t>2086; 5071</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2024; 4549</t>
+          <t>2014; 4549</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4513; 9379</t>
+          <t>4504; 9380</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12494; 16798</t>
+          <t>13030; 16798</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19164; 21668</t>
+          <t>18807; 21668</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17006; 22803</t>
+          <t>17007; 22803</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18540; 23098</t>
+          <t>18582; 23098</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32418; 38513</t>
+          <t>32484; 38602</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38830; 44216</t>
+          <t>38766; 44211</t>
         </is>
       </c>
     </row>
